--- a/docs/downloads/04/tbl_raisons_non_scol_alaotra_ambatomanga.xlsx
+++ b/docs/downloads/04/tbl_raisons_non_scol_alaotra_ambatomanga.xlsx
@@ -387,12 +387,6 @@
           <t>Autre raison</t>
         </is>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>33.3</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -405,12 +399,6 @@
           <t>Famine</t>
         </is>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>33.3</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -423,12 +411,6 @@
           <t>Trop jeune</t>
         </is>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>33.3</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -459,12 +441,6 @@
           <t>Besoin revenu</t>
         </is>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>4.2</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -477,12 +453,6 @@
           <t>Famine</t>
         </is>
       </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>8.300000000000001</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -495,12 +465,6 @@
           <t>Handicap / maladie</t>
         </is>
       </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>8.300000000000001</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -513,12 +477,6 @@
           <t>Main-d'oeuvre exploitation</t>
         </is>
       </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>4.2</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -531,12 +489,6 @@
           <t>Sans intérêt (famille)</t>
         </is>
       </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>4.2</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -566,12 +518,6 @@
         <is>
           <t>École trop éloignée</t>
         </is>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>4.2</v>
       </c>
     </row>
   </sheetData>
